--- a/ManpowerPython_BI.xlsx
+++ b/ManpowerPython_BI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aditya.pandey4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aditya.pandey4\Downloads\test_chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,16 +13,17 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet3!$A$1:$G$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet3!$A$1:$G$1842</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7707" uniqueCount="1800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8272" uniqueCount="1811">
   <si>
     <t>Supply Chain Centre-GRT Noida</t>
   </si>
@@ -5422,13 +5423,46 @@
   </si>
   <si>
     <t>Supply Chain Centre-Hyderabad_Security</t>
+  </si>
+  <si>
+    <t>SCC_Centre</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Female_count</t>
+  </si>
+  <si>
+    <t>Total Full Time</t>
+  </si>
+  <si>
+    <t>Total off-roll</t>
+  </si>
+  <si>
+    <t>Total Casual, HK, Security</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5440,6 +5474,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5477,7 +5518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5486,6 +5527,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5788,7 +5830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1764"/>
+  <dimension ref="A1:G1842"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.7265625" bestFit="1" customWidth="1"/>
@@ -46372,8 +46414,3941 @@
         <v>1799</v>
       </c>
     </row>
+    <row r="1765" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1765" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1765">
+        <v>122</v>
+      </c>
+      <c r="D1765" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1765">
+        <v>11</v>
+      </c>
+      <c r="F1765" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1765" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1766" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1766">
+        <v>28</v>
+      </c>
+      <c r="D1766" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1766">
+        <v>3</v>
+      </c>
+      <c r="F1766" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1766" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1767" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1767">
+        <v>25</v>
+      </c>
+      <c r="D1767" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E1767">
+        <v>6</v>
+      </c>
+      <c r="F1767" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1767" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1768" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1768">
+        <v>117</v>
+      </c>
+      <c r="D1768" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1768">
+        <v>13</v>
+      </c>
+      <c r="F1768" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1768" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1769" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1769">
+        <v>0</v>
+      </c>
+      <c r="D1769" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1769">
+        <v>0</v>
+      </c>
+      <c r="F1769" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1769" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1770" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1770">
+        <v>157</v>
+      </c>
+      <c r="D1770" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1770">
+        <v>56</v>
+      </c>
+      <c r="F1770" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1770" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1771" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1771">
+        <v>0</v>
+      </c>
+      <c r="D1771" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1771">
+        <v>0</v>
+      </c>
+      <c r="F1771" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1771" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1772" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1772">
+        <v>100</v>
+      </c>
+      <c r="D1772" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1772">
+        <v>22</v>
+      </c>
+      <c r="F1772" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1772" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1773" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1773">
+        <v>33</v>
+      </c>
+      <c r="D1773" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1773">
+        <v>2</v>
+      </c>
+      <c r="F1773" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1773" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1774" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1774">
+        <v>26</v>
+      </c>
+      <c r="D1774" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1774">
+        <v>2</v>
+      </c>
+      <c r="F1774" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1774" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1775" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1775">
+        <v>47</v>
+      </c>
+      <c r="D1775" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1775">
+        <v>6</v>
+      </c>
+      <c r="F1775" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1775" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1776" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1776">
+        <v>10</v>
+      </c>
+      <c r="D1776" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1776">
+        <v>1</v>
+      </c>
+      <c r="F1776" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1776" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1777" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1777">
+        <v>10</v>
+      </c>
+      <c r="D1777" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1777">
+        <v>1</v>
+      </c>
+      <c r="F1777" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1777" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1778" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1778">
+        <v>9</v>
+      </c>
+      <c r="D1778" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1778">
+        <v>1</v>
+      </c>
+      <c r="F1778" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1778" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1779" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1779">
+        <v>0</v>
+      </c>
+      <c r="D1779" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1779">
+        <v>0</v>
+      </c>
+      <c r="F1779" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1779" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1780" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1780">
+        <v>12</v>
+      </c>
+      <c r="D1780" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1780">
+        <v>0</v>
+      </c>
+      <c r="F1780" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1780" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1781" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1781">
+        <v>0</v>
+      </c>
+      <c r="D1781" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1781">
+        <v>0</v>
+      </c>
+      <c r="F1781" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1781" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1782" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1782">
+        <v>31</v>
+      </c>
+      <c r="D1782" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1782">
+        <v>9</v>
+      </c>
+      <c r="F1782" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1782" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1783" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1783">
+        <v>10</v>
+      </c>
+      <c r="D1783" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1783">
+        <v>4</v>
+      </c>
+      <c r="F1783" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1783" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1784" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1784">
+        <v>10</v>
+      </c>
+      <c r="D1784" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1784">
+        <v>1</v>
+      </c>
+      <c r="F1784" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1784" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1785" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1785">
+        <v>60</v>
+      </c>
+      <c r="D1785" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1785">
+        <v>6</v>
+      </c>
+      <c r="F1785" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1785" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1786" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1786">
+        <v>17</v>
+      </c>
+      <c r="D1786" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1786">
+        <v>3</v>
+      </c>
+      <c r="F1786" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1786" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1787" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1787">
+        <v>13</v>
+      </c>
+      <c r="D1787" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1787">
+        <v>1</v>
+      </c>
+      <c r="F1787" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1787" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1788" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1788">
+        <v>12</v>
+      </c>
+      <c r="D1788" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1788">
+        <v>2</v>
+      </c>
+      <c r="F1788" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1788" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1789" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1789">
+        <v>0</v>
+      </c>
+      <c r="D1789" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1789">
+        <v>0</v>
+      </c>
+      <c r="F1789" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1789" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1790" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1790">
+        <v>11</v>
+      </c>
+      <c r="D1790" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1790">
+        <v>3</v>
+      </c>
+      <c r="F1790" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1790" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1791" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1791">
+        <v>0</v>
+      </c>
+      <c r="D1791" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1791">
+        <v>0</v>
+      </c>
+      <c r="F1791" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1791" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1792" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1792">
+        <v>70</v>
+      </c>
+      <c r="D1792" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1792">
+        <v>1</v>
+      </c>
+      <c r="F1792" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1792" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1793" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1793">
+        <v>14</v>
+      </c>
+      <c r="D1793" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1793">
+        <v>5</v>
+      </c>
+      <c r="F1793" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1793" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1794" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1794">
+        <v>15</v>
+      </c>
+      <c r="D1794" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1794">
+        <v>2</v>
+      </c>
+      <c r="F1794" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1794" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1795" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1795">
+        <v>19</v>
+      </c>
+      <c r="D1795" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1795">
+        <v>2</v>
+      </c>
+      <c r="F1795" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1795" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1796" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1796">
+        <v>6</v>
+      </c>
+      <c r="D1796" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1796">
+        <v>1</v>
+      </c>
+      <c r="F1796" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1796" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1797" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1797">
+        <v>8</v>
+      </c>
+      <c r="D1797" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1797">
+        <v>0</v>
+      </c>
+      <c r="F1797" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1797" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1798" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1798">
+        <v>17</v>
+      </c>
+      <c r="D1798" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1798">
+        <v>5</v>
+      </c>
+      <c r="F1798" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1798" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1799" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1799">
+        <v>0</v>
+      </c>
+      <c r="D1799" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1799">
+        <v>0</v>
+      </c>
+      <c r="F1799" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1799" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1800" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1800">
+        <v>2</v>
+      </c>
+      <c r="D1800" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1800">
+        <v>0</v>
+      </c>
+      <c r="F1800" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1800" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1801" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1801">
+        <v>0</v>
+      </c>
+      <c r="D1801" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1801">
+        <v>0</v>
+      </c>
+      <c r="F1801" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1801" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1802" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1802">
+        <v>32</v>
+      </c>
+      <c r="D1802" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1802">
+        <v>7</v>
+      </c>
+      <c r="F1802" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1802" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1803" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1803">
+        <v>7</v>
+      </c>
+      <c r="D1803" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1803">
+        <v>3</v>
+      </c>
+      <c r="F1803" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1803" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1804" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1804" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1804">
+        <v>6</v>
+      </c>
+      <c r="D1804" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1804">
+        <v>2</v>
+      </c>
+      <c r="F1804" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1804" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1805" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1805">
+        <v>43</v>
+      </c>
+      <c r="D1805" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1805">
+        <v>4</v>
+      </c>
+      <c r="F1805" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1805" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1806" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1806">
+        <v>7</v>
+      </c>
+      <c r="D1806" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1806">
+        <v>1</v>
+      </c>
+      <c r="F1806" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1806" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1807" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1807" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1807">
+        <v>11</v>
+      </c>
+      <c r="D1807" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1807">
+        <v>1</v>
+      </c>
+      <c r="F1807" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1807" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1808" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1808" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1808">
+        <v>11</v>
+      </c>
+      <c r="D1808" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1808">
+        <v>1</v>
+      </c>
+      <c r="F1808" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1808" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1809" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1809" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1809">
+        <v>17</v>
+      </c>
+      <c r="D1809" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1809">
+        <v>1</v>
+      </c>
+      <c r="F1809" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1809" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1810" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1810" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1810">
+        <v>25</v>
+      </c>
+      <c r="D1810" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1810">
+        <v>5</v>
+      </c>
+      <c r="F1810" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1810" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1811" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1811" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1811">
+        <v>7</v>
+      </c>
+      <c r="D1811" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1811">
+        <v>1</v>
+      </c>
+      <c r="F1811" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1811" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1812" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1812" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1812">
+        <v>10</v>
+      </c>
+      <c r="D1812" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1812">
+        <v>2</v>
+      </c>
+      <c r="F1812" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1812" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1813" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1813" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1813">
+        <v>17</v>
+      </c>
+      <c r="D1813" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1813">
+        <v>3</v>
+      </c>
+      <c r="F1813" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1813" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1814" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1814" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1814">
+        <v>6</v>
+      </c>
+      <c r="D1814" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1814">
+        <v>0</v>
+      </c>
+      <c r="F1814" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1814" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1815" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1815" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1815">
+        <v>2</v>
+      </c>
+      <c r="D1815" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1815">
+        <v>0</v>
+      </c>
+      <c r="F1815" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1815" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1816" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1816" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1816">
+        <v>4</v>
+      </c>
+      <c r="D1816" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1816">
+        <v>1</v>
+      </c>
+      <c r="F1816" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1816" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1817" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1817" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1817">
+        <v>0</v>
+      </c>
+      <c r="D1817" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1817">
+        <v>0</v>
+      </c>
+      <c r="F1817" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1817" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1818" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1818" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1818">
+        <v>8</v>
+      </c>
+      <c r="D1818" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1818">
+        <v>2</v>
+      </c>
+      <c r="F1818" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1818" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1819" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1819" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1819">
+        <v>0</v>
+      </c>
+      <c r="D1819" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1819">
+        <v>0</v>
+      </c>
+      <c r="F1819" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1819" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1820" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1820" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1820">
+        <v>23</v>
+      </c>
+      <c r="D1820" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1820">
+        <v>0</v>
+      </c>
+      <c r="F1820" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1820" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1821" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1821">
+        <v>5</v>
+      </c>
+      <c r="D1821" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1821">
+        <v>1</v>
+      </c>
+      <c r="F1821" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1821" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1822" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1822" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1822">
+        <v>6</v>
+      </c>
+      <c r="D1822" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1822">
+        <v>1</v>
+      </c>
+      <c r="F1822" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1822" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1823" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1823" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1823">
+        <v>127</v>
+      </c>
+      <c r="D1823" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1823">
+        <v>23</v>
+      </c>
+      <c r="F1823" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1823" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1824" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1824" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1824">
+        <v>34</v>
+      </c>
+      <c r="D1824" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1824">
+        <v>7</v>
+      </c>
+      <c r="F1824" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1824" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1825" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1825" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1825">
+        <v>31</v>
+      </c>
+      <c r="D1825" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1825">
+        <v>4</v>
+      </c>
+      <c r="F1825" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1825" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1826" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1826" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1826">
+        <v>49</v>
+      </c>
+      <c r="D1826" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1826">
+        <v>10</v>
+      </c>
+      <c r="F1826" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1826" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1827" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1827" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1827">
+        <v>0</v>
+      </c>
+      <c r="D1827" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1827">
+        <v>0</v>
+      </c>
+      <c r="F1827" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1827" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1828" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1828" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1828">
+        <v>161</v>
+      </c>
+      <c r="D1828" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1828">
+        <v>76</v>
+      </c>
+      <c r="F1828" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1828" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1829" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1829" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1829">
+        <v>0</v>
+      </c>
+      <c r="D1829" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1829">
+        <v>0</v>
+      </c>
+      <c r="F1829" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1829" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1830" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1830" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1830">
+        <v>200</v>
+      </c>
+      <c r="D1830" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1830">
+        <v>15</v>
+      </c>
+      <c r="F1830" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1830" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1831" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1831" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1831">
+        <v>45</v>
+      </c>
+      <c r="D1831" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1831">
+        <v>30</v>
+      </c>
+      <c r="F1831" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1831" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1832" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1832" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1832">
+        <v>23</v>
+      </c>
+      <c r="D1832" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1832">
+        <v>6</v>
+      </c>
+      <c r="F1832" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1832" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1833" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1833" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1833">
+        <v>23</v>
+      </c>
+      <c r="D1833" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1833">
+        <v>2</v>
+      </c>
+      <c r="F1833" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1833" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1834" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1834" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1834">
+        <v>6</v>
+      </c>
+      <c r="D1834" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1834">
+        <v>1</v>
+      </c>
+      <c r="F1834" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1834" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1835" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1835" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1835">
+        <v>7</v>
+      </c>
+      <c r="D1835" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1835">
+        <v>1</v>
+      </c>
+      <c r="F1835" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1835" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1836" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1836" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1836">
+        <v>18</v>
+      </c>
+      <c r="D1836" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1836">
+        <v>1</v>
+      </c>
+      <c r="F1836" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1836" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1837" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1837" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1837">
+        <v>0</v>
+      </c>
+      <c r="D1837" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1837">
+        <v>0</v>
+      </c>
+      <c r="F1837" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1837" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1838" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1838" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1838">
+        <v>4</v>
+      </c>
+      <c r="D1838" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1838">
+        <v>0</v>
+      </c>
+      <c r="F1838" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1838" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1839" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1839" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1839">
+        <v>1</v>
+      </c>
+      <c r="D1839" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1839">
+        <v>1</v>
+      </c>
+      <c r="F1839" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1839" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1840" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1840" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1840">
+        <v>50</v>
+      </c>
+      <c r="D1840" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1840">
+        <v>30</v>
+      </c>
+      <c r="F1840" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1840" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1841" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1841" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1841">
+        <v>5</v>
+      </c>
+      <c r="D1841" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1841">
+        <v>4</v>
+      </c>
+      <c r="F1841" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1841" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1842" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1842" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1842">
+        <v>7</v>
+      </c>
+      <c r="D1842" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1842">
+        <v>1</v>
+      </c>
+      <c r="F1842" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1842" t="s">
+        <v>1799</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E125"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>45323</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>122</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>45323</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>45323</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>25</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>45323</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D5">
+        <v>175</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>45323</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>117</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>45323</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>45323</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>157</v>
+      </c>
+      <c r="E8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>45323</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>45323</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D10">
+        <v>274</v>
+      </c>
+      <c r="E10">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>45323</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>45323</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>45323</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>26</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <v>45323</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D14">
+        <v>159</v>
+      </c>
+      <c r="E14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>45323</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D15">
+        <v>608</v>
+      </c>
+      <c r="E15">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>45323</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>47</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>45323</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>45323</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>45323</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D19">
+        <v>67</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <v>45323</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>9</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>45323</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <v>45323</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23">
+        <v>45323</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>45323</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D24">
+        <v>21</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>45323</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>31</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26">
+        <v>45323</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27">
+        <v>45323</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28">
+        <v>45323</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D28">
+        <v>51</v>
+      </c>
+      <c r="E28">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29">
+        <v>45323</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D29">
+        <v>139</v>
+      </c>
+      <c r="E29">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30">
+        <v>45323</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>60</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31">
+        <v>45323</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>17</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32">
+        <v>45323</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>13</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33">
+        <v>45323</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D33">
+        <v>90</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34">
+        <v>45323</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35">
+        <v>45323</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36">
+        <v>45323</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36">
+        <v>11</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37">
+        <v>45323</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38">
+        <v>45323</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D38">
+        <v>23</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39">
+        <v>45323</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39">
+        <v>70</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40">
+        <v>45323</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>14</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41">
+        <v>45323</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41">
+        <v>15</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42">
+        <v>45323</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D42">
+        <v>99</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43">
+        <v>45323</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D43">
+        <v>212</v>
+      </c>
+      <c r="E43">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44">
+        <v>45323</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>19</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45">
+        <v>45323</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46">
+        <v>45323</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>8</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47">
+        <v>45323</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D47">
+        <v>33</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48">
+        <v>45323</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48">
+        <v>17</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49">
+        <v>45323</v>
+      </c>
+      <c r="C49" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50">
+        <v>45323</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51">
+        <v>45323</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52">
+        <v>45323</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D52">
+        <v>19</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53">
+        <v>45323</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>32</v>
+      </c>
+      <c r="E53">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54">
+        <v>45323</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>7</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55">
+        <v>45323</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56">
+        <v>45323</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D56">
+        <v>45</v>
+      </c>
+      <c r="E56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57">
+        <v>45323</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D57">
+        <v>97</v>
+      </c>
+      <c r="E57">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58">
+        <v>45323</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>43</v>
+      </c>
+      <c r="E58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59">
+        <v>45323</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>7</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60">
+        <v>45323</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60">
+        <v>11</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61">
+        <v>45323</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D61">
+        <v>61</v>
+      </c>
+      <c r="E61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62">
+        <v>45323</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62">
+        <v>11</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63">
+        <v>45323</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63">
+        <v>17</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64">
+        <v>45323</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D64">
+        <v>28</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65">
+        <v>45323</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65">
+        <v>25</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66">
+        <v>45323</v>
+      </c>
+      <c r="C66" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66">
+        <v>7</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67">
+        <v>45323</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67">
+        <v>10</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68">
+        <v>45323</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D68">
+        <v>42</v>
+      </c>
+      <c r="E68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69">
+        <v>45323</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D69">
+        <v>131</v>
+      </c>
+      <c r="E69">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70">
+        <v>45323</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>17</v>
+      </c>
+      <c r="E70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71">
+        <v>45323</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71">
+        <v>6</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72">
+        <v>45323</v>
+      </c>
+      <c r="C72" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>16</v>
+      </c>
+      <c r="B73">
+        <v>45323</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D73">
+        <v>25</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74">
+        <v>45323</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75">
+        <v>45323</v>
+      </c>
+      <c r="C75" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76">
+        <v>45323</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76">
+        <v>8</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77">
+        <v>45323</v>
+      </c>
+      <c r="C77" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78">
+        <v>45323</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D78">
+        <v>12</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79">
+        <v>45323</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79">
+        <v>23</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80">
+        <v>45323</v>
+      </c>
+      <c r="C80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81">
+        <v>45323</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>16</v>
+      </c>
+      <c r="B82">
+        <v>45323</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D82">
+        <v>34</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83">
+        <v>45323</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D83">
+        <v>71</v>
+      </c>
+      <c r="E83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>17</v>
+      </c>
+      <c r="B84">
+        <v>45323</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>127</v>
+      </c>
+      <c r="E84">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>17</v>
+      </c>
+      <c r="B85">
+        <v>45323</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85">
+        <v>34</v>
+      </c>
+      <c r="E85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>17</v>
+      </c>
+      <c r="B86">
+        <v>45323</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86">
+        <v>31</v>
+      </c>
+      <c r="E86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87">
+        <v>45323</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D87">
+        <v>192</v>
+      </c>
+      <c r="E87">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88">
+        <v>45323</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88">
+        <v>49</v>
+      </c>
+      <c r="E88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>17</v>
+      </c>
+      <c r="B89">
+        <v>45323</v>
+      </c>
+      <c r="C89" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90">
+        <v>45323</v>
+      </c>
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90">
+        <v>161</v>
+      </c>
+      <c r="E90">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91">
+        <v>45323</v>
+      </c>
+      <c r="C91" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92">
+        <v>45323</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D92">
+        <v>210</v>
+      </c>
+      <c r="E92">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93">
+        <v>45323</v>
+      </c>
+      <c r="C93" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93">
+        <v>200</v>
+      </c>
+      <c r="E93">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94">
+        <v>45323</v>
+      </c>
+      <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94">
+        <v>45</v>
+      </c>
+      <c r="E94">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95">
+        <v>45323</v>
+      </c>
+      <c r="C95" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95">
+        <v>23</v>
+      </c>
+      <c r="E95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96">
+        <v>45323</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D96">
+        <v>268</v>
+      </c>
+      <c r="E96">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97">
+        <v>45323</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D97">
+        <v>670</v>
+      </c>
+      <c r="E97">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>18</v>
+      </c>
+      <c r="B98">
+        <v>45323</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>23</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>18</v>
+      </c>
+      <c r="B99">
+        <v>45323</v>
+      </c>
+      <c r="C99" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>6</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>18</v>
+      </c>
+      <c r="B100">
+        <v>45323</v>
+      </c>
+      <c r="C100" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100">
+        <v>7</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>18</v>
+      </c>
+      <c r="B101">
+        <v>45323</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D101">
+        <v>36</v>
+      </c>
+      <c r="E101">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>18</v>
+      </c>
+      <c r="B102">
+        <v>45323</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102">
+        <v>18</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103">
+        <v>45323</v>
+      </c>
+      <c r="C103" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104">
+        <v>45323</v>
+      </c>
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104">
+        <v>4</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>18</v>
+      </c>
+      <c r="B105">
+        <v>45323</v>
+      </c>
+      <c r="C105" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106">
+        <v>45323</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D106">
+        <v>23</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>18</v>
+      </c>
+      <c r="B107">
+        <v>45323</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107">
+        <v>50</v>
+      </c>
+      <c r="E107">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>18</v>
+      </c>
+      <c r="B108">
+        <v>45323</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108">
+        <v>5</v>
+      </c>
+      <c r="E108">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>18</v>
+      </c>
+      <c r="B109">
+        <v>45323</v>
+      </c>
+      <c r="C109" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109">
+        <v>7</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>18</v>
+      </c>
+      <c r="B110">
+        <v>45323</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D110">
+        <v>62</v>
+      </c>
+      <c r="E110">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>18</v>
+      </c>
+      <c r="B111">
+        <v>45323</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D111">
+        <v>121</v>
+      </c>
+      <c r="E111">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B112">
+        <v>45323</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>458</v>
+      </c>
+      <c r="E112">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B113">
+        <v>45323</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113">
+        <v>114</v>
+      </c>
+      <c r="E113">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B114">
+        <v>45323</v>
+      </c>
+      <c r="C114" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114">
+        <v>107</v>
+      </c>
+      <c r="E114">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B115">
+        <v>45323</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D115">
+        <v>679</v>
+      </c>
+      <c r="E115">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B116">
+        <v>45323</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116">
+        <v>237</v>
+      </c>
+      <c r="E116">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B117">
+        <v>45323</v>
+      </c>
+      <c r="C117" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B118">
+        <v>45323</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118">
+        <v>372</v>
+      </c>
+      <c r="E118">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B119">
+        <v>45323</v>
+      </c>
+      <c r="C119" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B120">
+        <v>45323</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D120">
+        <v>610</v>
+      </c>
+      <c r="E120">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B121">
+        <v>45323</v>
+      </c>
+      <c r="C121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121">
+        <v>531</v>
+      </c>
+      <c r="E121">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B122">
+        <v>45323</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122">
+        <v>126</v>
+      </c>
+      <c r="E122">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B123">
+        <v>45323</v>
+      </c>
+      <c r="C123" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123">
+        <v>103</v>
+      </c>
+      <c r="E123">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B124">
+        <v>45323</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D124">
+        <v>760</v>
+      </c>
+      <c r="E124">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B125">
+        <v>45323</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D125">
+        <v>2049</v>
+      </c>
+      <c r="E125">
+        <v>417</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>